--- a/plan.xlsx
+++ b/plan.xlsx
@@ -867,10 +867,10 @@
     <xf borderId="5" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -885,7 +885,7 @@
     <xf borderId="5" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1909,7 +1909,7 @@
       <c r="A29" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="19" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="21"/>
@@ -1987,7 +1987,7 @@
       <c r="A32" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="42" t="s">
+      <c r="B32" s="41" t="s">
         <v>51</v>
       </c>
       <c r="C32" s="29"/>
@@ -2143,7 +2143,7 @@
       <c r="A38" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="42" t="s">
+      <c r="B38" s="41" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="29"/>
@@ -2247,7 +2247,7 @@
       <c r="A42" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B42" s="41" t="s">
+      <c r="B42" s="42" t="s">
         <v>67</v>
       </c>
       <c r="C42" s="21"/>
@@ -2507,7 +2507,7 @@
       <c r="A52" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="43" t="s">
+      <c r="B52" s="46" t="s">
         <v>87</v>
       </c>
       <c r="C52" s="21"/>
@@ -2559,7 +2559,7 @@
       <c r="A54" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="41" t="s">
+      <c r="B54" s="19" t="s">
         <v>91</v>
       </c>
       <c r="C54" s="21"/>
@@ -2767,7 +2767,7 @@
       <c r="A62" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="B62" s="43" t="s">
+      <c r="B62" s="46" t="s">
         <v>107</v>
       </c>
       <c r="C62" s="49"/>
@@ -3443,7 +3443,7 @@
       <c r="A88" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="B88" s="41" t="s">
+      <c r="B88" s="42" t="s">
         <v>159</v>
       </c>
       <c r="C88" s="21"/>
